--- a/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
+++ b/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2BDD74-D3EB-4C2F-8515-813FEFE541F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33722AB-E14C-428C-9DEF-00ACA87EE150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="7" r:id="rId1"/>
@@ -161,14 +161,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -429,15 +426,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -746,18 +743,18 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -765,7 +762,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2669,7 +2666,7 @@
         <f t="shared" si="3"/>
         <v>1.1976131001942825</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <f t="shared" si="4"/>
         <v>1.1079655842353593</v>
       </c>
@@ -3821,7 +3818,7 @@
         <f t="shared" si="3"/>
         <v>1.2189347486437045</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <f t="shared" si="4"/>
         <v>1.1285870188193361</v>
       </c>

--- a/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
+++ b/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33722AB-E14C-428C-9DEF-00ACA87EE150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFBC93F-15CC-4E8A-B56A-2E518D94D37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="7" r:id="rId1"/>

--- a/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
+++ b/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BFBC93F-15CC-4E8A-B56A-2E518D94D37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2190DFB8-25DB-4A54-AA59-34CFA01B2EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="7" r:id="rId1"/>

--- a/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
+++ b/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2190DFB8-25DB-4A54-AA59-34CFA01B2EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AD5063-4570-4281-949D-EFD520465851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="7" r:id="rId1"/>
     <sheet name="CA" sheetId="4" r:id="rId2"/>
     <sheet name="BLS_National" sheetId="5" r:id="rId3"/>
     <sheet name="BLS_West" sheetId="6" r:id="rId4"/>
+    <sheet name="BLS_West monthly" sheetId="8" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="320">
   <si>
     <t>Year</t>
   </si>
@@ -106,6 +107,921 @@
   </si>
   <si>
     <t>CA</t>
+  </si>
+  <si>
+    <t>Month/Year Date</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>CPI</t>
+  </si>
+  <si>
+    <t>CPI Adjusted (2022)</t>
+  </si>
+  <si>
+    <t>Jan-1998</t>
+  </si>
+  <si>
+    <t>Feb-1998</t>
+  </si>
+  <si>
+    <t>Mar-1998</t>
+  </si>
+  <si>
+    <t>Apr-1998</t>
+  </si>
+  <si>
+    <t>May-1998</t>
+  </si>
+  <si>
+    <t>Jun-1998</t>
+  </si>
+  <si>
+    <t>Jul-1998</t>
+  </si>
+  <si>
+    <t>Aug-1998</t>
+  </si>
+  <si>
+    <t>Sep-1998</t>
+  </si>
+  <si>
+    <t>Oct-1998</t>
+  </si>
+  <si>
+    <t>Nov-1998</t>
+  </si>
+  <si>
+    <t>Dec-1998</t>
+  </si>
+  <si>
+    <t>Jan-1999</t>
+  </si>
+  <si>
+    <t>Feb-1999</t>
+  </si>
+  <si>
+    <t>Mar-1999</t>
+  </si>
+  <si>
+    <t>Apr-1999</t>
+  </si>
+  <si>
+    <t>May-1999</t>
+  </si>
+  <si>
+    <t>Jun-1999</t>
+  </si>
+  <si>
+    <t>Jul-1999</t>
+  </si>
+  <si>
+    <t>Aug-1999</t>
+  </si>
+  <si>
+    <t>Sep-1999</t>
+  </si>
+  <si>
+    <t>Oct-1999</t>
+  </si>
+  <si>
+    <t>Nov-1999</t>
+  </si>
+  <si>
+    <t>Dec-1999</t>
+  </si>
+  <si>
+    <t>Jan-2000</t>
+  </si>
+  <si>
+    <t>Feb-2000</t>
+  </si>
+  <si>
+    <t>Mar-2000</t>
+  </si>
+  <si>
+    <t>Apr-2000</t>
+  </si>
+  <si>
+    <t>May-2000</t>
+  </si>
+  <si>
+    <t>Jun-2000</t>
+  </si>
+  <si>
+    <t>Jul-2000</t>
+  </si>
+  <si>
+    <t>Aug-2000</t>
+  </si>
+  <si>
+    <t>Sep-2000</t>
+  </si>
+  <si>
+    <t>Oct-2000</t>
+  </si>
+  <si>
+    <t>Nov-2000</t>
+  </si>
+  <si>
+    <t>Dec-2000</t>
+  </si>
+  <si>
+    <t>Jan-2001</t>
+  </si>
+  <si>
+    <t>Feb-2001</t>
+  </si>
+  <si>
+    <t>Mar-2001</t>
+  </si>
+  <si>
+    <t>Apr-2001</t>
+  </si>
+  <si>
+    <t>May-2001</t>
+  </si>
+  <si>
+    <t>Jun-2001</t>
+  </si>
+  <si>
+    <t>Jul-2001</t>
+  </si>
+  <si>
+    <t>Aug-2001</t>
+  </si>
+  <si>
+    <t>Sep-2001</t>
+  </si>
+  <si>
+    <t>Oct-2001</t>
+  </si>
+  <si>
+    <t>Nov-2001</t>
+  </si>
+  <si>
+    <t>Dec-2001</t>
+  </si>
+  <si>
+    <t>Jan-2002</t>
+  </si>
+  <si>
+    <t>Feb-2002</t>
+  </si>
+  <si>
+    <t>Mar-2002</t>
+  </si>
+  <si>
+    <t>Apr-2002</t>
+  </si>
+  <si>
+    <t>May-2002</t>
+  </si>
+  <si>
+    <t>Jun-2002</t>
+  </si>
+  <si>
+    <t>Jul-2002</t>
+  </si>
+  <si>
+    <t>Aug-2002</t>
+  </si>
+  <si>
+    <t>Sep-2002</t>
+  </si>
+  <si>
+    <t>Oct-2002</t>
+  </si>
+  <si>
+    <t>Nov-2002</t>
+  </si>
+  <si>
+    <t>Dec-2002</t>
+  </si>
+  <si>
+    <t>Jan-2003</t>
+  </si>
+  <si>
+    <t>Feb-2003</t>
+  </si>
+  <si>
+    <t>Mar-2003</t>
+  </si>
+  <si>
+    <t>Apr-2003</t>
+  </si>
+  <si>
+    <t>May-2003</t>
+  </si>
+  <si>
+    <t>Jun-2003</t>
+  </si>
+  <si>
+    <t>Jul-2003</t>
+  </si>
+  <si>
+    <t>Aug-2003</t>
+  </si>
+  <si>
+    <t>Sep-2003</t>
+  </si>
+  <si>
+    <t>Oct-2003</t>
+  </si>
+  <si>
+    <t>Nov-2003</t>
+  </si>
+  <si>
+    <t>Dec-2003</t>
+  </si>
+  <si>
+    <t>Jan-2004</t>
+  </si>
+  <si>
+    <t>Feb-2004</t>
+  </si>
+  <si>
+    <t>Mar-2004</t>
+  </si>
+  <si>
+    <t>Apr-2004</t>
+  </si>
+  <si>
+    <t>May-2004</t>
+  </si>
+  <si>
+    <t>Jun-2004</t>
+  </si>
+  <si>
+    <t>Jul-2004</t>
+  </si>
+  <si>
+    <t>Aug-2004</t>
+  </si>
+  <si>
+    <t>Sep-2004</t>
+  </si>
+  <si>
+    <t>Oct-2004</t>
+  </si>
+  <si>
+    <t>Nov-2004</t>
+  </si>
+  <si>
+    <t>Dec-2004</t>
+  </si>
+  <si>
+    <t>Jan-2005</t>
+  </si>
+  <si>
+    <t>Feb-2005</t>
+  </si>
+  <si>
+    <t>Mar-2005</t>
+  </si>
+  <si>
+    <t>Apr-2005</t>
+  </si>
+  <si>
+    <t>May-2005</t>
+  </si>
+  <si>
+    <t>Jun-2005</t>
+  </si>
+  <si>
+    <t>Jul-2005</t>
+  </si>
+  <si>
+    <t>Aug-2005</t>
+  </si>
+  <si>
+    <t>Sep-2005</t>
+  </si>
+  <si>
+    <t>Oct-2005</t>
+  </si>
+  <si>
+    <t>Nov-2005</t>
+  </si>
+  <si>
+    <t>Dec-2005</t>
+  </si>
+  <si>
+    <t>Jan-2006</t>
+  </si>
+  <si>
+    <t>Feb-2006</t>
+  </si>
+  <si>
+    <t>Mar-2006</t>
+  </si>
+  <si>
+    <t>Apr-2006</t>
+  </si>
+  <si>
+    <t>May-2006</t>
+  </si>
+  <si>
+    <t>Jun-2006</t>
+  </si>
+  <si>
+    <t>Jul-2006</t>
+  </si>
+  <si>
+    <t>Aug-2006</t>
+  </si>
+  <si>
+    <t>Sep-2006</t>
+  </si>
+  <si>
+    <t>Oct-2006</t>
+  </si>
+  <si>
+    <t>Nov-2006</t>
+  </si>
+  <si>
+    <t>Dec-2006</t>
+  </si>
+  <si>
+    <t>Jan-2007</t>
+  </si>
+  <si>
+    <t>Feb-2007</t>
+  </si>
+  <si>
+    <t>Mar-2007</t>
+  </si>
+  <si>
+    <t>Apr-2007</t>
+  </si>
+  <si>
+    <t>May-2007</t>
+  </si>
+  <si>
+    <t>Jun-2007</t>
+  </si>
+  <si>
+    <t>Jul-2007</t>
+  </si>
+  <si>
+    <t>Aug-2007</t>
+  </si>
+  <si>
+    <t>Sep-2007</t>
+  </si>
+  <si>
+    <t>Oct-2007</t>
+  </si>
+  <si>
+    <t>Nov-2007</t>
+  </si>
+  <si>
+    <t>Dec-2007</t>
+  </si>
+  <si>
+    <t>Jan-2008</t>
+  </si>
+  <si>
+    <t>Feb-2008</t>
+  </si>
+  <si>
+    <t>Mar-2008</t>
+  </si>
+  <si>
+    <t>Apr-2008</t>
+  </si>
+  <si>
+    <t>May-2008</t>
+  </si>
+  <si>
+    <t>Jun-2008</t>
+  </si>
+  <si>
+    <t>Jul-2008</t>
+  </si>
+  <si>
+    <t>Aug-2008</t>
+  </si>
+  <si>
+    <t>Sep-2008</t>
+  </si>
+  <si>
+    <t>Oct-2008</t>
+  </si>
+  <si>
+    <t>Nov-2008</t>
+  </si>
+  <si>
+    <t>Dec-2008</t>
+  </si>
+  <si>
+    <t>Jan-2009</t>
+  </si>
+  <si>
+    <t>Feb-2009</t>
+  </si>
+  <si>
+    <t>Mar-2009</t>
+  </si>
+  <si>
+    <t>Apr-2009</t>
+  </si>
+  <si>
+    <t>May-2009</t>
+  </si>
+  <si>
+    <t>Jun-2009</t>
+  </si>
+  <si>
+    <t>Jul-2009</t>
+  </si>
+  <si>
+    <t>Aug-2009</t>
+  </si>
+  <si>
+    <t>Sep-2009</t>
+  </si>
+  <si>
+    <t>Oct-2009</t>
+  </si>
+  <si>
+    <t>Nov-2009</t>
+  </si>
+  <si>
+    <t>Dec-2009</t>
+  </si>
+  <si>
+    <t>Jan-2010</t>
+  </si>
+  <si>
+    <t>Feb-2010</t>
+  </si>
+  <si>
+    <t>Mar-2010</t>
+  </si>
+  <si>
+    <t>Apr-2010</t>
+  </si>
+  <si>
+    <t>May-2010</t>
+  </si>
+  <si>
+    <t>Jun-2010</t>
+  </si>
+  <si>
+    <t>Jul-2010</t>
+  </si>
+  <si>
+    <t>Aug-2010</t>
+  </si>
+  <si>
+    <t>Sep-2010</t>
+  </si>
+  <si>
+    <t>Oct-2010</t>
+  </si>
+  <si>
+    <t>Nov-2010</t>
+  </si>
+  <si>
+    <t>Dec-2010</t>
+  </si>
+  <si>
+    <t>Jan-2011</t>
+  </si>
+  <si>
+    <t>Feb-2011</t>
+  </si>
+  <si>
+    <t>Mar-2011</t>
+  </si>
+  <si>
+    <t>Apr-2011</t>
+  </si>
+  <si>
+    <t>May-2011</t>
+  </si>
+  <si>
+    <t>Jun-2011</t>
+  </si>
+  <si>
+    <t>Jul-2011</t>
+  </si>
+  <si>
+    <t>Aug-2011</t>
+  </si>
+  <si>
+    <t>Sep-2011</t>
+  </si>
+  <si>
+    <t>Oct-2011</t>
+  </si>
+  <si>
+    <t>Nov-2011</t>
+  </si>
+  <si>
+    <t>Dec-2011</t>
+  </si>
+  <si>
+    <t>Jan-2012</t>
+  </si>
+  <si>
+    <t>Feb-2012</t>
+  </si>
+  <si>
+    <t>Mar-2012</t>
+  </si>
+  <si>
+    <t>Apr-2012</t>
+  </si>
+  <si>
+    <t>May-2012</t>
+  </si>
+  <si>
+    <t>Jun-2012</t>
+  </si>
+  <si>
+    <t>Jul-2012</t>
+  </si>
+  <si>
+    <t>Aug-2012</t>
+  </si>
+  <si>
+    <t>Sep-2012</t>
+  </si>
+  <si>
+    <t>Oct-2012</t>
+  </si>
+  <si>
+    <t>Nov-2012</t>
+  </si>
+  <si>
+    <t>Dec-2012</t>
+  </si>
+  <si>
+    <t>Jan-2013</t>
+  </si>
+  <si>
+    <t>Feb-2013</t>
+  </si>
+  <si>
+    <t>Mar-2013</t>
+  </si>
+  <si>
+    <t>Apr-2013</t>
+  </si>
+  <si>
+    <t>May-2013</t>
+  </si>
+  <si>
+    <t>Jun-2013</t>
+  </si>
+  <si>
+    <t>Jul-2013</t>
+  </si>
+  <si>
+    <t>Aug-2013</t>
+  </si>
+  <si>
+    <t>Sep-2013</t>
+  </si>
+  <si>
+    <t>Oct-2013</t>
+  </si>
+  <si>
+    <t>Nov-2013</t>
+  </si>
+  <si>
+    <t>Dec-2013</t>
+  </si>
+  <si>
+    <t>Jan-2014</t>
+  </si>
+  <si>
+    <t>Feb-2014</t>
+  </si>
+  <si>
+    <t>Mar-2014</t>
+  </si>
+  <si>
+    <t>Apr-2014</t>
+  </si>
+  <si>
+    <t>May-2014</t>
+  </si>
+  <si>
+    <t>Jun-2014</t>
+  </si>
+  <si>
+    <t>Jul-2014</t>
+  </si>
+  <si>
+    <t>Aug-2014</t>
+  </si>
+  <si>
+    <t>Sep-2014</t>
+  </si>
+  <si>
+    <t>Oct-2014</t>
+  </si>
+  <si>
+    <t>Nov-2014</t>
+  </si>
+  <si>
+    <t>Dec-2014</t>
+  </si>
+  <si>
+    <t>Jan-2015</t>
+  </si>
+  <si>
+    <t>Feb-2015</t>
+  </si>
+  <si>
+    <t>Mar-2015</t>
+  </si>
+  <si>
+    <t>Apr-2015</t>
+  </si>
+  <si>
+    <t>May-2015</t>
+  </si>
+  <si>
+    <t>Jun-2015</t>
+  </si>
+  <si>
+    <t>Jul-2015</t>
+  </si>
+  <si>
+    <t>Aug-2015</t>
+  </si>
+  <si>
+    <t>Sep-2015</t>
+  </si>
+  <si>
+    <t>Oct-2015</t>
+  </si>
+  <si>
+    <t>Nov-2015</t>
+  </si>
+  <si>
+    <t>Dec-2015</t>
+  </si>
+  <si>
+    <t>Jan-2016</t>
+  </si>
+  <si>
+    <t>Feb-2016</t>
+  </si>
+  <si>
+    <t>Mar-2016</t>
+  </si>
+  <si>
+    <t>Apr-2016</t>
+  </si>
+  <si>
+    <t>May-2016</t>
+  </si>
+  <si>
+    <t>Jun-2016</t>
+  </si>
+  <si>
+    <t>Jul-2016</t>
+  </si>
+  <si>
+    <t>Aug-2016</t>
+  </si>
+  <si>
+    <t>Sep-2016</t>
+  </si>
+  <si>
+    <t>Oct-2016</t>
+  </si>
+  <si>
+    <t>Nov-2016</t>
+  </si>
+  <si>
+    <t>Dec-2016</t>
+  </si>
+  <si>
+    <t>Jan-2017</t>
+  </si>
+  <si>
+    <t>Feb-2017</t>
+  </si>
+  <si>
+    <t>Mar-2017</t>
+  </si>
+  <si>
+    <t>Apr-2017</t>
+  </si>
+  <si>
+    <t>May-2017</t>
+  </si>
+  <si>
+    <t>Jun-2017</t>
+  </si>
+  <si>
+    <t>Jul-2017</t>
+  </si>
+  <si>
+    <t>Aug-2017</t>
+  </si>
+  <si>
+    <t>Sep-2017</t>
+  </si>
+  <si>
+    <t>Oct-2017</t>
+  </si>
+  <si>
+    <t>Nov-2017</t>
+  </si>
+  <si>
+    <t>Dec-2017</t>
+  </si>
+  <si>
+    <t>Jan-2018</t>
+  </si>
+  <si>
+    <t>Feb-2018</t>
+  </si>
+  <si>
+    <t>Mar-2018</t>
+  </si>
+  <si>
+    <t>Apr-2018</t>
+  </si>
+  <si>
+    <t>May-2018</t>
+  </si>
+  <si>
+    <t>Jun-2018</t>
+  </si>
+  <si>
+    <t>Jul-2018</t>
+  </si>
+  <si>
+    <t>Aug-2018</t>
+  </si>
+  <si>
+    <t>Sep-2018</t>
+  </si>
+  <si>
+    <t>Oct-2018</t>
+  </si>
+  <si>
+    <t>Nov-2018</t>
+  </si>
+  <si>
+    <t>Dec-2018</t>
+  </si>
+  <si>
+    <t>Jan-2019</t>
+  </si>
+  <si>
+    <t>Feb-2019</t>
+  </si>
+  <si>
+    <t>Mar-2019</t>
+  </si>
+  <si>
+    <t>Apr-2019</t>
+  </si>
+  <si>
+    <t>May-2019</t>
+  </si>
+  <si>
+    <t>Jun-2019</t>
+  </si>
+  <si>
+    <t>Jul-2019</t>
+  </si>
+  <si>
+    <t>Aug-2019</t>
+  </si>
+  <si>
+    <t>Sep-2019</t>
+  </si>
+  <si>
+    <t>Oct-2019</t>
+  </si>
+  <si>
+    <t>Nov-2019</t>
+  </si>
+  <si>
+    <t>Dec-2019</t>
+  </si>
+  <si>
+    <t>Jan-2020</t>
+  </si>
+  <si>
+    <t>Feb-2020</t>
+  </si>
+  <si>
+    <t>Mar-2020</t>
+  </si>
+  <si>
+    <t>Apr-2020</t>
+  </si>
+  <si>
+    <t>May-2020</t>
+  </si>
+  <si>
+    <t>Jun-2020</t>
+  </si>
+  <si>
+    <t>Jul-2020</t>
+  </si>
+  <si>
+    <t>Aug-2020</t>
+  </si>
+  <si>
+    <t>Sep-2020</t>
+  </si>
+  <si>
+    <t>Oct-2020</t>
+  </si>
+  <si>
+    <t>Nov-2020</t>
+  </si>
+  <si>
+    <t>Dec-2020</t>
+  </si>
+  <si>
+    <t>Jan-2021</t>
+  </si>
+  <si>
+    <t>Feb-2021</t>
+  </si>
+  <si>
+    <t>Mar-2021</t>
+  </si>
+  <si>
+    <t>Apr-2021</t>
+  </si>
+  <si>
+    <t>May-2021</t>
+  </si>
+  <si>
+    <t>Jun-2021</t>
+  </si>
+  <si>
+    <t>Jul-2021</t>
+  </si>
+  <si>
+    <t>Aug-2021</t>
+  </si>
+  <si>
+    <t>Sep-2021</t>
+  </si>
+  <si>
+    <t>Oct-2021</t>
+  </si>
+  <si>
+    <t>Nov-2021</t>
+  </si>
+  <si>
+    <t>Dec-2021</t>
+  </si>
+  <si>
+    <t>Jan-2022</t>
+  </si>
+  <si>
+    <t>Feb-2022</t>
+  </si>
+  <si>
+    <t>Mar-2022</t>
+  </si>
+  <si>
+    <t>Apr-2022</t>
+  </si>
+  <si>
+    <t>May-2022</t>
+  </si>
+  <si>
+    <t>Jun-2022</t>
+  </si>
+  <si>
+    <t>Jul-2022</t>
+  </si>
+  <si>
+    <t>Aug-2022</t>
+  </si>
+  <si>
+    <t>Sep-2022</t>
+  </si>
+  <si>
+    <t>Oct-2022</t>
+  </si>
+  <si>
+    <t>Nov-2022</t>
+  </si>
+  <si>
+    <t>Dec-2022</t>
+  </si>
+  <si>
+    <t>Jan-2023</t>
   </si>
 </sst>
 </file>
@@ -4305,4 +5221,4245 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8329967B-C8B7-48FF-A0D9-55D2F3AE9026}">
+  <dimension ref="A1:D302"/>
+  <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="4" max="4" width="17.59765625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2">
+        <v>35796</v>
+      </c>
+      <c r="C2">
+        <v>163</v>
+      </c>
+      <c r="D2">
+        <v>0.513423019620319</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3">
+        <v>35827</v>
+      </c>
+      <c r="C3">
+        <v>163.19999999999999</v>
+      </c>
+      <c r="D3">
+        <v>0.51405298651555864</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>35855</v>
+      </c>
+      <c r="C4">
+        <v>163.30000000000001</v>
+      </c>
+      <c r="D4">
+        <v>0.51436796996317846</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>35886</v>
+      </c>
+      <c r="C5">
+        <v>163.6</v>
+      </c>
+      <c r="D5">
+        <v>0.51531292030603792</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6">
+        <v>35916</v>
+      </c>
+      <c r="C6">
+        <v>164.3</v>
+      </c>
+      <c r="D6">
+        <v>0.51751780443937678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7">
+        <v>35947</v>
+      </c>
+      <c r="C7">
+        <v>164.2</v>
+      </c>
+      <c r="D7">
+        <v>0.51720282099175685</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8">
+        <v>35977</v>
+      </c>
+      <c r="C8">
+        <v>164.3</v>
+      </c>
+      <c r="D8">
+        <v>0.51751780443937678</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9">
+        <v>36008</v>
+      </c>
+      <c r="C9">
+        <v>164.8</v>
+      </c>
+      <c r="D9">
+        <v>0.51909272167747589</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10">
+        <v>36039</v>
+      </c>
+      <c r="C10">
+        <v>165.1</v>
+      </c>
+      <c r="D10">
+        <v>0.52003767202033535</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11">
+        <v>36069</v>
+      </c>
+      <c r="C11">
+        <v>165.5</v>
+      </c>
+      <c r="D11">
+        <v>0.52129760581081463</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12">
+        <v>36100</v>
+      </c>
+      <c r="C12">
+        <v>165.8</v>
+      </c>
+      <c r="D12">
+        <v>0.52224255615367421</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13">
+        <v>36130</v>
+      </c>
+      <c r="C13">
+        <v>165.8</v>
+      </c>
+      <c r="D13">
+        <v>0.52224255615367421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>36161</v>
+      </c>
+      <c r="C14">
+        <v>166.4</v>
+      </c>
+      <c r="D14">
+        <v>0.52413245683939313</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15">
+        <v>36192</v>
+      </c>
+      <c r="C15">
+        <v>166.9</v>
+      </c>
+      <c r="D15">
+        <v>0.52570737407749224</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>36220</v>
+      </c>
+      <c r="C16">
+        <v>167.3</v>
+      </c>
+      <c r="D16">
+        <v>0.52696730786797163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17">
+        <v>36251</v>
+      </c>
+      <c r="C17">
+        <v>169</v>
+      </c>
+      <c r="D17">
+        <v>0.5323220264775087</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18">
+        <v>36281</v>
+      </c>
+      <c r="C18">
+        <v>168.7</v>
+      </c>
+      <c r="D18">
+        <v>0.53137707613464913</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19">
+        <v>36312</v>
+      </c>
+      <c r="C19">
+        <v>168.3</v>
+      </c>
+      <c r="D19">
+        <v>0.53011714234416984</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20">
+        <v>36342</v>
+      </c>
+      <c r="C20">
+        <v>168.9</v>
+      </c>
+      <c r="D20">
+        <v>0.53200704302988888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21">
+        <v>36373</v>
+      </c>
+      <c r="C21">
+        <v>169.5</v>
+      </c>
+      <c r="D21">
+        <v>0.53389694371560781</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22">
+        <v>36404</v>
+      </c>
+      <c r="C22">
+        <v>170</v>
+      </c>
+      <c r="D22">
+        <v>0.53547186095370691</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23">
+        <v>36434</v>
+      </c>
+      <c r="C23">
+        <v>170.4</v>
+      </c>
+      <c r="D23">
+        <v>0.53673179474418631</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24">
+        <v>36465</v>
+      </c>
+      <c r="C24">
+        <v>170.4</v>
+      </c>
+      <c r="D24">
+        <v>0.53673179474418631</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B25">
+        <v>36495</v>
+      </c>
+      <c r="C25">
+        <v>170.5</v>
+      </c>
+      <c r="D25">
+        <v>0.53704677819180602</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26">
+        <v>36526</v>
+      </c>
+      <c r="C26">
+        <v>171</v>
+      </c>
+      <c r="D26">
+        <v>0.53862169542990523</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B27">
+        <v>36557</v>
+      </c>
+      <c r="C27">
+        <v>172</v>
+      </c>
+      <c r="D27">
+        <v>0.54177152990610344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28">
+        <v>36586</v>
+      </c>
+      <c r="C28">
+        <v>173.5</v>
+      </c>
+      <c r="D28">
+        <v>0.54649628162040087</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29">
+        <v>36617</v>
+      </c>
+      <c r="C29">
+        <v>173.7</v>
+      </c>
+      <c r="D29">
+        <v>0.54712624851564051</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30">
+        <v>36647</v>
+      </c>
+      <c r="C30">
+        <v>174</v>
+      </c>
+      <c r="D30">
+        <v>0.54807119885849997</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31">
+        <v>36678</v>
+      </c>
+      <c r="C31">
+        <v>174.3</v>
+      </c>
+      <c r="D31">
+        <v>0.54901614920135955</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32">
+        <v>36708</v>
+      </c>
+      <c r="C32">
+        <v>175.2</v>
+      </c>
+      <c r="D32">
+        <v>0.55185100022993794</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>50</v>
+      </c>
+      <c r="B33">
+        <v>36739</v>
+      </c>
+      <c r="C33">
+        <v>175.9</v>
+      </c>
+      <c r="D33">
+        <v>0.5540558843632768</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>51</v>
+      </c>
+      <c r="B34">
+        <v>36770</v>
+      </c>
+      <c r="C34">
+        <v>176.6</v>
+      </c>
+      <c r="D34">
+        <v>0.55626076849661554</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35">
+        <v>36800</v>
+      </c>
+      <c r="C35">
+        <v>177.2</v>
+      </c>
+      <c r="D35">
+        <v>0.55815066918233447</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36">
+        <v>36831</v>
+      </c>
+      <c r="C36">
+        <v>177.2</v>
+      </c>
+      <c r="D36">
+        <v>0.55815066918233447</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37">
+        <v>36861</v>
+      </c>
+      <c r="C37">
+        <v>177.1</v>
+      </c>
+      <c r="D37">
+        <v>0.55783568573471465</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38">
+        <v>36892</v>
+      </c>
+      <c r="C38">
+        <v>178.3</v>
+      </c>
+      <c r="D38">
+        <v>0.56161548710615261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>56</v>
+      </c>
+      <c r="B39">
+        <v>36923</v>
+      </c>
+      <c r="C39">
+        <v>179.3</v>
+      </c>
+      <c r="D39">
+        <v>0.56476532158235093</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40">
+        <v>36951</v>
+      </c>
+      <c r="C40">
+        <v>180.1</v>
+      </c>
+      <c r="D40">
+        <v>0.5672851891633095</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41">
+        <v>36982</v>
+      </c>
+      <c r="C41">
+        <v>180.4</v>
+      </c>
+      <c r="D41">
+        <v>0.56823013950616896</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>59</v>
+      </c>
+      <c r="B42">
+        <v>37012</v>
+      </c>
+      <c r="C42">
+        <v>181.3</v>
+      </c>
+      <c r="D42">
+        <v>0.57106499053474746</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B43">
+        <v>37043</v>
+      </c>
+      <c r="C43">
+        <v>182</v>
+      </c>
+      <c r="D43">
+        <v>0.57326987466808621</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44">
+        <v>37073</v>
+      </c>
+      <c r="C44">
+        <v>182</v>
+      </c>
+      <c r="D44">
+        <v>0.57326987466808621</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45">
+        <v>37104</v>
+      </c>
+      <c r="C45">
+        <v>181.9</v>
+      </c>
+      <c r="D45">
+        <v>0.57295489122046639</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>63</v>
+      </c>
+      <c r="B46">
+        <v>37135</v>
+      </c>
+      <c r="C46">
+        <v>182.5</v>
+      </c>
+      <c r="D46">
+        <v>0.57484479190618543</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+      <c r="B47">
+        <v>37165</v>
+      </c>
+      <c r="C47">
+        <v>182.5</v>
+      </c>
+      <c r="D47">
+        <v>0.57484479190618543</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48">
+        <v>37196</v>
+      </c>
+      <c r="C48">
+        <v>182.3</v>
+      </c>
+      <c r="D48">
+        <v>0.57421482501094578</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>66</v>
+      </c>
+      <c r="B49">
+        <v>37226</v>
+      </c>
+      <c r="C49">
+        <v>181.6</v>
+      </c>
+      <c r="D49">
+        <v>0.57200994087760693</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50">
+        <v>37257</v>
+      </c>
+      <c r="C50">
+        <v>182.4</v>
+      </c>
+      <c r="D50">
+        <v>0.57452980845856561</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51">
+        <v>37288</v>
+      </c>
+      <c r="C51">
+        <v>183.2</v>
+      </c>
+      <c r="D51">
+        <v>0.57704967603952417</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52">
+        <v>37316</v>
+      </c>
+      <c r="C52">
+        <v>184</v>
+      </c>
+      <c r="D52">
+        <v>0.57956954362048274</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>70</v>
+      </c>
+      <c r="B53">
+        <v>37347</v>
+      </c>
+      <c r="C53">
+        <v>185.1</v>
+      </c>
+      <c r="D53">
+        <v>0.58303436154430088</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>71</v>
+      </c>
+      <c r="B54">
+        <v>37377</v>
+      </c>
+      <c r="C54">
+        <v>184.8</v>
+      </c>
+      <c r="D54">
+        <v>0.58208941120144142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B55">
+        <v>37408</v>
+      </c>
+      <c r="C55">
+        <v>184.5</v>
+      </c>
+      <c r="D55">
+        <v>0.58114446085858196</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>73</v>
+      </c>
+      <c r="B56">
+        <v>37438</v>
+      </c>
+      <c r="C56">
+        <v>184.7</v>
+      </c>
+      <c r="D56">
+        <v>0.5817744277538216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>74</v>
+      </c>
+      <c r="B57">
+        <v>37469</v>
+      </c>
+      <c r="C57">
+        <v>185.3</v>
+      </c>
+      <c r="D57">
+        <v>0.58366432843954064</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>75</v>
+      </c>
+      <c r="B58">
+        <v>37500</v>
+      </c>
+      <c r="C58">
+        <v>185.7</v>
+      </c>
+      <c r="D58">
+        <v>0.58492426223001981</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>76</v>
+      </c>
+      <c r="B59">
+        <v>37530</v>
+      </c>
+      <c r="C59">
+        <v>185.8</v>
+      </c>
+      <c r="D59">
+        <v>0.58523924567763974</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>77</v>
+      </c>
+      <c r="B60">
+        <v>37561</v>
+      </c>
+      <c r="C60">
+        <v>185.8</v>
+      </c>
+      <c r="D60">
+        <v>0.58523924567763974</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61">
+        <v>37591</v>
+      </c>
+      <c r="C61">
+        <v>185.5</v>
+      </c>
+      <c r="D61">
+        <v>0.58429429533478017</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62">
+        <v>37622</v>
+      </c>
+      <c r="C62">
+        <v>186.6</v>
+      </c>
+      <c r="D62">
+        <v>0.58775911325859831</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63">
+        <v>37653</v>
+      </c>
+      <c r="C63">
+        <v>188.1</v>
+      </c>
+      <c r="D63">
+        <v>0.59248386497289574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>81</v>
+      </c>
+      <c r="B64">
+        <v>37681</v>
+      </c>
+      <c r="C64">
+        <v>189.3</v>
+      </c>
+      <c r="D64">
+        <v>0.5962636663443337</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>82</v>
+      </c>
+      <c r="B65">
+        <v>37712</v>
+      </c>
+      <c r="C65">
+        <v>188.8</v>
+      </c>
+      <c r="D65">
+        <v>0.59468874910623459</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66">
+        <v>37742</v>
+      </c>
+      <c r="C66">
+        <v>188.5</v>
+      </c>
+      <c r="D66">
+        <v>0.59374379876337502</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67">
+        <v>37773</v>
+      </c>
+      <c r="C67">
+        <v>188.1</v>
+      </c>
+      <c r="D67">
+        <v>0.59248386497289574</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68">
+        <v>37803</v>
+      </c>
+      <c r="C68">
+        <v>188.4</v>
+      </c>
+      <c r="D68">
+        <v>0.5934288153157552</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>86</v>
+      </c>
+      <c r="B69">
+        <v>37834</v>
+      </c>
+      <c r="C69">
+        <v>189.2</v>
+      </c>
+      <c r="D69">
+        <v>0.59594868289671377</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70">
+        <v>37865</v>
+      </c>
+      <c r="C70">
+        <v>189.6</v>
+      </c>
+      <c r="D70">
+        <v>0.59720861668719316</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71">
+        <v>37895</v>
+      </c>
+      <c r="C71">
+        <v>189.4</v>
+      </c>
+      <c r="D71">
+        <v>0.59657864979195352</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72">
+        <v>37926</v>
+      </c>
+      <c r="C72">
+        <v>188.5</v>
+      </c>
+      <c r="D72">
+        <v>0.59374379876337502</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>90</v>
+      </c>
+      <c r="B73">
+        <v>37956</v>
+      </c>
+      <c r="C73">
+        <v>188.3</v>
+      </c>
+      <c r="D73">
+        <v>0.59311383186813538</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74">
+        <v>37987</v>
+      </c>
+      <c r="C74">
+        <v>189.4</v>
+      </c>
+      <c r="D74">
+        <v>0.59657864979195352</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75">
+        <v>38018</v>
+      </c>
+      <c r="C75">
+        <v>190.8</v>
+      </c>
+      <c r="D75">
+        <v>0.60098841805863112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76">
+        <v>38047</v>
+      </c>
+      <c r="C76">
+        <v>192.2</v>
+      </c>
+      <c r="D76">
+        <v>0.60539818632530862</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>94</v>
+      </c>
+      <c r="B77">
+        <v>38078</v>
+      </c>
+      <c r="C77">
+        <v>192.3</v>
+      </c>
+      <c r="D77">
+        <v>0.60571316977292855</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>95</v>
+      </c>
+      <c r="B78">
+        <v>38108</v>
+      </c>
+      <c r="C78">
+        <v>193.4</v>
+      </c>
+      <c r="D78">
+        <v>0.60917798769674658</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>96</v>
+      </c>
+      <c r="B79">
+        <v>38139</v>
+      </c>
+      <c r="C79">
+        <v>193.3</v>
+      </c>
+      <c r="D79">
+        <v>0.60886300424912676</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>97</v>
+      </c>
+      <c r="B80">
+        <v>38169</v>
+      </c>
+      <c r="C80">
+        <v>192.9</v>
+      </c>
+      <c r="D80">
+        <v>0.60760307045864748</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>98</v>
+      </c>
+      <c r="B81">
+        <v>38200</v>
+      </c>
+      <c r="C81">
+        <v>193</v>
+      </c>
+      <c r="D81">
+        <v>0.6079180539062673</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>99</v>
+      </c>
+      <c r="B82">
+        <v>38231</v>
+      </c>
+      <c r="C82">
+        <v>193.8</v>
+      </c>
+      <c r="D82">
+        <v>0.61043792148722598</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>100</v>
+      </c>
+      <c r="B83">
+        <v>38261</v>
+      </c>
+      <c r="C83">
+        <v>195</v>
+      </c>
+      <c r="D83">
+        <v>0.61421772285866383</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84">
+        <v>38292</v>
+      </c>
+      <c r="C84">
+        <v>195.1</v>
+      </c>
+      <c r="D84">
+        <v>0.61453270630628365</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>102</v>
+      </c>
+      <c r="B85">
+        <v>38322</v>
+      </c>
+      <c r="C85">
+        <v>194.2</v>
+      </c>
+      <c r="D85">
+        <v>0.61169785527770515</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>103</v>
+      </c>
+      <c r="B86">
+        <v>38353</v>
+      </c>
+      <c r="C86">
+        <v>194.5</v>
+      </c>
+      <c r="D86">
+        <v>0.61264280562056472</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>104</v>
+      </c>
+      <c r="B87">
+        <v>38384</v>
+      </c>
+      <c r="C87">
+        <v>195.7</v>
+      </c>
+      <c r="D87">
+        <v>0.61642260699200258</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>105</v>
+      </c>
+      <c r="B88">
+        <v>38412</v>
+      </c>
+      <c r="C88">
+        <v>197.1</v>
+      </c>
+      <c r="D88">
+        <v>0.62083237525868018</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>106</v>
+      </c>
+      <c r="B89">
+        <v>38443</v>
+      </c>
+      <c r="C89">
+        <v>198.6</v>
+      </c>
+      <c r="D89">
+        <v>0.62555712697297761</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>107</v>
+      </c>
+      <c r="B90">
+        <v>38473</v>
+      </c>
+      <c r="C90">
+        <v>198.8</v>
+      </c>
+      <c r="D90">
+        <v>0.62618709386821736</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>108</v>
+      </c>
+      <c r="B91">
+        <v>38504</v>
+      </c>
+      <c r="C91">
+        <v>198</v>
+      </c>
+      <c r="D91">
+        <v>0.62366722628725868</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>109</v>
+      </c>
+      <c r="B92">
+        <v>38534</v>
+      </c>
+      <c r="C92">
+        <v>198.6</v>
+      </c>
+      <c r="D92">
+        <v>0.62555712697297761</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>110</v>
+      </c>
+      <c r="B93">
+        <v>38565</v>
+      </c>
+      <c r="C93">
+        <v>199.6</v>
+      </c>
+      <c r="D93">
+        <v>0.62870696144917593</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94">
+        <v>38596</v>
+      </c>
+      <c r="C94">
+        <v>201.7</v>
+      </c>
+      <c r="D94">
+        <v>0.63532161384919228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>112</v>
+      </c>
+      <c r="B95">
+        <v>38626</v>
+      </c>
+      <c r="C95">
+        <v>202.6</v>
+      </c>
+      <c r="D95">
+        <v>0.63815646487777067</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>113</v>
+      </c>
+      <c r="B96">
+        <v>38657</v>
+      </c>
+      <c r="C96">
+        <v>201.4</v>
+      </c>
+      <c r="D96">
+        <v>0.63437666350633282</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>114</v>
+      </c>
+      <c r="B97">
+        <v>38687</v>
+      </c>
+      <c r="C97">
+        <v>200</v>
+      </c>
+      <c r="D97">
+        <v>0.62996689523965521</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>115</v>
+      </c>
+      <c r="B98">
+        <v>38718</v>
+      </c>
+      <c r="C98">
+        <v>201.7</v>
+      </c>
+      <c r="D98">
+        <v>0.63532161384919228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>116</v>
+      </c>
+      <c r="B99">
+        <v>38749</v>
+      </c>
+      <c r="C99">
+        <v>202.7</v>
+      </c>
+      <c r="D99">
+        <v>0.63847144832539049</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>117</v>
+      </c>
+      <c r="B100">
+        <v>38777</v>
+      </c>
+      <c r="C100">
+        <v>203.8</v>
+      </c>
+      <c r="D100">
+        <v>0.64193626624920874</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>118</v>
+      </c>
+      <c r="B101">
+        <v>38808</v>
+      </c>
+      <c r="C101">
+        <v>205.3</v>
+      </c>
+      <c r="D101">
+        <v>0.64666101796350606</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>119</v>
+      </c>
+      <c r="B102">
+        <v>38838</v>
+      </c>
+      <c r="C102">
+        <v>206.9</v>
+      </c>
+      <c r="D102">
+        <v>0.6517007531254233</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>120</v>
+      </c>
+      <c r="B103">
+        <v>38869</v>
+      </c>
+      <c r="C103">
+        <v>206.4</v>
+      </c>
+      <c r="D103">
+        <v>0.6501258358873242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>121</v>
+      </c>
+      <c r="B104">
+        <v>38899</v>
+      </c>
+      <c r="C104">
+        <v>206.7</v>
+      </c>
+      <c r="D104">
+        <v>0.65107078623018366</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>122</v>
+      </c>
+      <c r="B105">
+        <v>38930</v>
+      </c>
+      <c r="C105">
+        <v>207.5</v>
+      </c>
+      <c r="D105">
+        <v>0.65359065381114223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>123</v>
+      </c>
+      <c r="B106">
+        <v>38961</v>
+      </c>
+      <c r="C106">
+        <v>207.8</v>
+      </c>
+      <c r="D106">
+        <v>0.6545356041540018</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>124</v>
+      </c>
+      <c r="B107">
+        <v>38991</v>
+      </c>
+      <c r="C107">
+        <v>207.1</v>
+      </c>
+      <c r="D107">
+        <v>0.65233072002066295</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>125</v>
+      </c>
+      <c r="B108">
+        <v>39022</v>
+      </c>
+      <c r="C108">
+        <v>206.3</v>
+      </c>
+      <c r="D108">
+        <v>0.64981085243970438</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>126</v>
+      </c>
+      <c r="B109">
+        <v>39052</v>
+      </c>
+      <c r="C109">
+        <v>206.2</v>
+      </c>
+      <c r="D109">
+        <v>0.64949586899208445</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>127</v>
+      </c>
+      <c r="B110">
+        <v>39083</v>
+      </c>
+      <c r="C110">
+        <v>207.79</v>
+      </c>
+      <c r="D110">
+        <v>0.65450410580923979</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>128</v>
+      </c>
+      <c r="B111">
+        <v>39114</v>
+      </c>
+      <c r="C111">
+        <v>208.995</v>
+      </c>
+      <c r="D111">
+        <v>0.65829965635305876</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>129</v>
+      </c>
+      <c r="B112">
+        <v>39142</v>
+      </c>
+      <c r="C112">
+        <v>210.77799999999999</v>
+      </c>
+      <c r="D112">
+        <v>0.66391581122412024</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113">
+        <v>39173</v>
+      </c>
+      <c r="C113">
+        <v>212.036</v>
+      </c>
+      <c r="D113">
+        <v>0.6678783029951777</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>131</v>
+      </c>
+      <c r="B114">
+        <v>39203</v>
+      </c>
+      <c r="C114">
+        <v>213.06299999999999</v>
+      </c>
+      <c r="D114">
+        <v>0.67111318300223322</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>132</v>
+      </c>
+      <c r="B115">
+        <v>39234</v>
+      </c>
+      <c r="C115">
+        <v>212.68</v>
+      </c>
+      <c r="D115">
+        <v>0.66990679639784934</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116">
+        <v>39264</v>
+      </c>
+      <c r="C116">
+        <v>212.542</v>
+      </c>
+      <c r="D116">
+        <v>0.66947211924013394</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>134</v>
+      </c>
+      <c r="B117">
+        <v>39295</v>
+      </c>
+      <c r="C117">
+        <v>212.40600000000001</v>
+      </c>
+      <c r="D117">
+        <v>0.66904374175137105</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>135</v>
+      </c>
+      <c r="B118">
+        <v>39326</v>
+      </c>
+      <c r="C118">
+        <v>212.92</v>
+      </c>
+      <c r="D118">
+        <v>0.67066275667213693</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>136</v>
+      </c>
+      <c r="B119">
+        <v>39356</v>
+      </c>
+      <c r="C119">
+        <v>213.917</v>
+      </c>
+      <c r="D119">
+        <v>0.67380314164490662</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>137</v>
+      </c>
+      <c r="B120">
+        <v>39387</v>
+      </c>
+      <c r="C120">
+        <v>214.904</v>
+      </c>
+      <c r="D120">
+        <v>0.6769120282729143</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>138</v>
+      </c>
+      <c r="B121">
+        <v>39417</v>
+      </c>
+      <c r="C121">
+        <v>214.733</v>
+      </c>
+      <c r="D121">
+        <v>0.67637340657748446</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>139</v>
+      </c>
+      <c r="B122">
+        <v>39448</v>
+      </c>
+      <c r="C122">
+        <v>215.739</v>
+      </c>
+      <c r="D122">
+        <v>0.67954214006053992</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>140</v>
+      </c>
+      <c r="B123">
+        <v>39479</v>
+      </c>
+      <c r="C123">
+        <v>216.339</v>
+      </c>
+      <c r="D123">
+        <v>0.68143204074625885</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>141</v>
+      </c>
+      <c r="B124">
+        <v>39508</v>
+      </c>
+      <c r="C124">
+        <v>218.53299999999999</v>
+      </c>
+      <c r="D124">
+        <v>0.68834277758703777</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>142</v>
+      </c>
+      <c r="B125">
+        <v>39539</v>
+      </c>
+      <c r="C125">
+        <v>219.43700000000001</v>
+      </c>
+      <c r="D125">
+        <v>0.69119022795352114</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>143</v>
+      </c>
+      <c r="B126">
+        <v>39569</v>
+      </c>
+      <c r="C126">
+        <v>221.00899999999999</v>
+      </c>
+      <c r="D126">
+        <v>0.69614176775010472</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>144</v>
+      </c>
+      <c r="B127">
+        <v>39600</v>
+      </c>
+      <c r="C127">
+        <v>223.04</v>
+      </c>
+      <c r="D127">
+        <v>0.70253908157126344</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>145</v>
+      </c>
+      <c r="B128">
+        <v>39630</v>
+      </c>
+      <c r="C128">
+        <v>223.86699999999999</v>
+      </c>
+      <c r="D128">
+        <v>0.70514399468307942</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>146</v>
+      </c>
+      <c r="B129">
+        <v>39661</v>
+      </c>
+      <c r="C129">
+        <v>222.82300000000001</v>
+      </c>
+      <c r="D129">
+        <v>0.7018555674899285</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>147</v>
+      </c>
+      <c r="B130">
+        <v>39692</v>
+      </c>
+      <c r="C130">
+        <v>222.13200000000001</v>
+      </c>
+      <c r="D130">
+        <v>0.69967903186687541</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>148</v>
+      </c>
+      <c r="B131">
+        <v>39722</v>
+      </c>
+      <c r="C131">
+        <v>221.03399999999999</v>
+      </c>
+      <c r="D131">
+        <v>0.69622051361200976</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>149</v>
+      </c>
+      <c r="B132">
+        <v>39753</v>
+      </c>
+      <c r="C132">
+        <v>217.113</v>
+      </c>
+      <c r="D132">
+        <v>0.68387001263083635</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>150</v>
+      </c>
+      <c r="B133">
+        <v>39783</v>
+      </c>
+      <c r="C133">
+        <v>214.685</v>
+      </c>
+      <c r="D133">
+        <v>0.67622221452262687</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>151</v>
+      </c>
+      <c r="B134">
+        <v>39814</v>
+      </c>
+      <c r="C134">
+        <v>215.923</v>
+      </c>
+      <c r="D134">
+        <v>0.68012170960416041</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>152</v>
+      </c>
+      <c r="B135">
+        <v>39845</v>
+      </c>
+      <c r="C135">
+        <v>217.095</v>
+      </c>
+      <c r="D135">
+        <v>0.6838133156102647</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>153</v>
+      </c>
+      <c r="B136">
+        <v>39873</v>
+      </c>
+      <c r="C136">
+        <v>217.357</v>
+      </c>
+      <c r="D136">
+        <v>0.68463857224302871</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>154</v>
+      </c>
+      <c r="B137">
+        <v>39904</v>
+      </c>
+      <c r="C137">
+        <v>217.91</v>
+      </c>
+      <c r="D137">
+        <v>0.6863804307083663</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>155</v>
+      </c>
+      <c r="B138">
+        <v>39934</v>
+      </c>
+      <c r="C138">
+        <v>218.56700000000001</v>
+      </c>
+      <c r="D138">
+        <v>0.68844987195922858</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>156</v>
+      </c>
+      <c r="B139">
+        <v>39965</v>
+      </c>
+      <c r="C139">
+        <v>219.86500000000001</v>
+      </c>
+      <c r="D139">
+        <v>0.69253835710933398</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>157</v>
+      </c>
+      <c r="B140">
+        <v>39995</v>
+      </c>
+      <c r="C140">
+        <v>219.48400000000001</v>
+      </c>
+      <c r="D140">
+        <v>0.69133827017390248</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>158</v>
+      </c>
+      <c r="B141">
+        <v>40026</v>
+      </c>
+      <c r="C141">
+        <v>219.88399999999999</v>
+      </c>
+      <c r="D141">
+        <v>0.69259820396438165</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>159</v>
+      </c>
+      <c r="B142">
+        <v>40057</v>
+      </c>
+      <c r="C142">
+        <v>220.29400000000001</v>
+      </c>
+      <c r="D142">
+        <v>0.69388963609962306</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>160</v>
+      </c>
+      <c r="B143">
+        <v>40087</v>
+      </c>
+      <c r="C143">
+        <v>220.447</v>
+      </c>
+      <c r="D143">
+        <v>0.69437156077448137</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>161</v>
+      </c>
+      <c r="B144">
+        <v>40118</v>
+      </c>
+      <c r="C144">
+        <v>219.72800000000001</v>
+      </c>
+      <c r="D144">
+        <v>0.69210682978609483</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>162</v>
+      </c>
+      <c r="B145">
+        <v>40148</v>
+      </c>
+      <c r="C145">
+        <v>219.30699999999999</v>
+      </c>
+      <c r="D145">
+        <v>0.69078074947161527</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>163</v>
+      </c>
+      <c r="B146">
+        <v>40179</v>
+      </c>
+      <c r="C146">
+        <v>219.989</v>
+      </c>
+      <c r="D146">
+        <v>0.69292893658438259</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>164</v>
+      </c>
+      <c r="B147">
+        <v>40210</v>
+      </c>
+      <c r="C147">
+        <v>220.179</v>
+      </c>
+      <c r="D147">
+        <v>0.69352740513486022</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>165</v>
+      </c>
+      <c r="B148">
+        <v>40238</v>
+      </c>
+      <c r="C148">
+        <v>220.809</v>
+      </c>
+      <c r="D148">
+        <v>0.69551180085486508</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>166</v>
+      </c>
+      <c r="B149">
+        <v>40269</v>
+      </c>
+      <c r="C149">
+        <v>221.202</v>
+      </c>
+      <c r="D149">
+        <v>0.69674968580401109</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>167</v>
+      </c>
+      <c r="B150">
+        <v>40299</v>
+      </c>
+      <c r="C150">
+        <v>221.417</v>
+      </c>
+      <c r="D150">
+        <v>0.69742690021639364</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>168</v>
+      </c>
+      <c r="B151">
+        <v>40330</v>
+      </c>
+      <c r="C151">
+        <v>221.14699999999999</v>
+      </c>
+      <c r="D151">
+        <v>0.69657644490782011</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>169</v>
+      </c>
+      <c r="B152">
+        <v>40360</v>
+      </c>
+      <c r="C152">
+        <v>221.33099999999999</v>
+      </c>
+      <c r="D152">
+        <v>0.6971560144514406</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>170</v>
+      </c>
+      <c r="B153">
+        <v>40391</v>
+      </c>
+      <c r="C153">
+        <v>221.523</v>
+      </c>
+      <c r="D153">
+        <v>0.69776078267087072</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>171</v>
+      </c>
+      <c r="B154">
+        <v>40422</v>
+      </c>
+      <c r="C154">
+        <v>221.38399999999999</v>
+      </c>
+      <c r="D154">
+        <v>0.69732295567867908</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155">
+        <v>40452</v>
+      </c>
+      <c r="C155">
+        <v>221.708</v>
+      </c>
+      <c r="D155">
+        <v>0.69834350204896734</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>173</v>
+      </c>
+      <c r="B156">
+        <v>40483</v>
+      </c>
+      <c r="C156">
+        <v>221.67099999999999</v>
+      </c>
+      <c r="D156">
+        <v>0.69822695817334801</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>174</v>
+      </c>
+      <c r="B157">
+        <v>40513</v>
+      </c>
+      <c r="C157">
+        <v>222.08099999999999</v>
+      </c>
+      <c r="D157">
+        <v>0.69951839030858931</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>175</v>
+      </c>
+      <c r="B158">
+        <v>40544</v>
+      </c>
+      <c r="C158">
+        <v>223.149</v>
+      </c>
+      <c r="D158">
+        <v>0.70288241352916914</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>176</v>
+      </c>
+      <c r="B159">
+        <v>40575</v>
+      </c>
+      <c r="C159">
+        <v>224.43100000000001</v>
+      </c>
+      <c r="D159">
+        <v>0.70692050132765527</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160">
+        <v>40603</v>
+      </c>
+      <c r="C160">
+        <v>226.55799999999999</v>
+      </c>
+      <c r="D160">
+        <v>0.71362019925852904</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>178</v>
+      </c>
+      <c r="B161">
+        <v>40634</v>
+      </c>
+      <c r="C161">
+        <v>227.83699999999999</v>
+      </c>
+      <c r="D161">
+        <v>0.71764883755358655</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>179</v>
+      </c>
+      <c r="B162">
+        <v>40664</v>
+      </c>
+      <c r="C162">
+        <v>228.51599999999999</v>
+      </c>
+      <c r="D162">
+        <v>0.71978757516292524</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>180</v>
+      </c>
+      <c r="B163">
+        <v>40695</v>
+      </c>
+      <c r="C163">
+        <v>228.07499999999999</v>
+      </c>
+      <c r="D163">
+        <v>0.71839849815892176</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>181</v>
+      </c>
+      <c r="B164">
+        <v>40725</v>
+      </c>
+      <c r="C164">
+        <v>227.80500000000001</v>
+      </c>
+      <c r="D164">
+        <v>0.71754804285034834</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>182</v>
+      </c>
+      <c r="B165">
+        <v>40756</v>
+      </c>
+      <c r="C165">
+        <v>228.22200000000001</v>
+      </c>
+      <c r="D165">
+        <v>0.71886152382692303</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>183</v>
+      </c>
+      <c r="B166">
+        <v>40787</v>
+      </c>
+      <c r="C166">
+        <v>229.14699999999999</v>
+      </c>
+      <c r="D166">
+        <v>0.72177512071740635</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>184</v>
+      </c>
+      <c r="B167">
+        <v>40817</v>
+      </c>
+      <c r="C167">
+        <v>229.19499999999999</v>
+      </c>
+      <c r="D167">
+        <v>0.72192631277226382</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>185</v>
+      </c>
+      <c r="B168">
+        <v>40848</v>
+      </c>
+      <c r="C168">
+        <v>228.77099999999999</v>
+      </c>
+      <c r="D168">
+        <v>0.72059078295435575</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>186</v>
+      </c>
+      <c r="B169">
+        <v>40878</v>
+      </c>
+      <c r="C169">
+        <v>228.11699999999999</v>
+      </c>
+      <c r="D169">
+        <v>0.71853079120692209</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>187</v>
+      </c>
+      <c r="B170">
+        <v>40909</v>
+      </c>
+      <c r="C170">
+        <v>228.98</v>
+      </c>
+      <c r="D170">
+        <v>0.72124909835988116</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>188</v>
+      </c>
+      <c r="B171">
+        <v>40940</v>
+      </c>
+      <c r="C171">
+        <v>229.995</v>
+      </c>
+      <c r="D171">
+        <v>0.7244461803532225</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>189</v>
+      </c>
+      <c r="B172">
+        <v>40969</v>
+      </c>
+      <c r="C172">
+        <v>232.03899999999999</v>
+      </c>
+      <c r="D172">
+        <v>0.73088444202257175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>190</v>
+      </c>
+      <c r="B173">
+        <v>41000</v>
+      </c>
+      <c r="C173">
+        <v>232.56100000000001</v>
+      </c>
+      <c r="D173">
+        <v>0.73252865561914726</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>191</v>
+      </c>
+      <c r="B174">
+        <v>41030</v>
+      </c>
+      <c r="C174">
+        <v>233.053</v>
+      </c>
+      <c r="D174">
+        <v>0.73407837418143684</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175" t="s">
+        <v>192</v>
+      </c>
+      <c r="B175">
+        <v>41061</v>
+      </c>
+      <c r="C175">
+        <v>232.70099999999999</v>
+      </c>
+      <c r="D175">
+        <v>0.73296963244581503</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176" t="s">
+        <v>193</v>
+      </c>
+      <c r="B176">
+        <v>41091</v>
+      </c>
+      <c r="C176">
+        <v>231.893</v>
+      </c>
+      <c r="D176">
+        <v>0.73042456618904683</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177" t="s">
+        <v>194</v>
+      </c>
+      <c r="B177">
+        <v>41122</v>
+      </c>
+      <c r="C177">
+        <v>233.001</v>
+      </c>
+      <c r="D177">
+        <v>0.7339145827886745</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178" t="s">
+        <v>195</v>
+      </c>
+      <c r="B178">
+        <v>41153</v>
+      </c>
+      <c r="C178">
+        <v>234.083</v>
+      </c>
+      <c r="D178">
+        <v>0.73732270369192099</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179" t="s">
+        <v>196</v>
+      </c>
+      <c r="B179">
+        <v>41183</v>
+      </c>
+      <c r="C179">
+        <v>234.96600000000001</v>
+      </c>
+      <c r="D179">
+        <v>0.7401040075344042</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180" t="s">
+        <v>197</v>
+      </c>
+      <c r="B180">
+        <v>41214</v>
+      </c>
+      <c r="C180">
+        <v>233.20599999999999</v>
+      </c>
+      <c r="D180">
+        <v>0.73456029885629515</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>198</v>
+      </c>
+      <c r="B181">
+        <v>41244</v>
+      </c>
+      <c r="C181">
+        <v>232.029</v>
+      </c>
+      <c r="D181">
+        <v>0.73085294367780973</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
+        <v>199</v>
+      </c>
+      <c r="B182">
+        <v>41275</v>
+      </c>
+      <c r="C182">
+        <v>232.75899999999999</v>
+      </c>
+      <c r="D182">
+        <v>0.73315232284543452</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183" t="s">
+        <v>200</v>
+      </c>
+      <c r="B183">
+        <v>41306</v>
+      </c>
+      <c r="C183">
+        <v>234.595</v>
+      </c>
+      <c r="D183">
+        <v>0.7389354189437346</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184" t="s">
+        <v>201</v>
+      </c>
+      <c r="B184">
+        <v>41334</v>
+      </c>
+      <c r="C184">
+        <v>235.511</v>
+      </c>
+      <c r="D184">
+        <v>0.74182066732393215</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185" t="s">
+        <v>202</v>
+      </c>
+      <c r="B185">
+        <v>41365</v>
+      </c>
+      <c r="C185">
+        <v>235.488</v>
+      </c>
+      <c r="D185">
+        <v>0.7417482211309796</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>203</v>
+      </c>
+      <c r="B186">
+        <v>41395</v>
+      </c>
+      <c r="C186">
+        <v>235.97900000000001</v>
+      </c>
+      <c r="D186">
+        <v>0.74329478985879305</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187" t="s">
+        <v>204</v>
+      </c>
+      <c r="B187">
+        <v>41426</v>
+      </c>
+      <c r="C187">
+        <v>236.227</v>
+      </c>
+      <c r="D187">
+        <v>0.74407594880889016</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188" t="s">
+        <v>205</v>
+      </c>
+      <c r="B188">
+        <v>41456</v>
+      </c>
+      <c r="C188">
+        <v>236.34100000000001</v>
+      </c>
+      <c r="D188">
+        <v>0.74443502993917676</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189" t="s">
+        <v>206</v>
+      </c>
+      <c r="B189">
+        <v>41487</v>
+      </c>
+      <c r="C189">
+        <v>236.59100000000001</v>
+      </c>
+      <c r="D189">
+        <v>0.74522248855822637</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190" t="s">
+        <v>207</v>
+      </c>
+      <c r="B190">
+        <v>41518</v>
+      </c>
+      <c r="C190">
+        <v>237.14599999999999</v>
+      </c>
+      <c r="D190">
+        <v>0.74697064669251634</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191" t="s">
+        <v>208</v>
+      </c>
+      <c r="B191">
+        <v>41548</v>
+      </c>
+      <c r="C191">
+        <v>237</v>
+      </c>
+      <c r="D191">
+        <v>0.74651077085899142</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192" t="s">
+        <v>209</v>
+      </c>
+      <c r="B192">
+        <v>41579</v>
+      </c>
+      <c r="C192">
+        <v>236.15299999999999</v>
+      </c>
+      <c r="D192">
+        <v>0.74384286105765141</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193" t="s">
+        <v>210</v>
+      </c>
+      <c r="B193">
+        <v>41609</v>
+      </c>
+      <c r="C193">
+        <v>236.096</v>
+      </c>
+      <c r="D193">
+        <v>0.74366332049250816</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194" t="s">
+        <v>211</v>
+      </c>
+      <c r="B194">
+        <v>41640</v>
+      </c>
+      <c r="C194">
+        <v>236.70699999999999</v>
+      </c>
+      <c r="D194">
+        <v>0.74558786935746535</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195" t="s">
+        <v>212</v>
+      </c>
+      <c r="B195">
+        <v>41671</v>
+      </c>
+      <c r="C195">
+        <v>237.614</v>
+      </c>
+      <c r="D195">
+        <v>0.74844476922737713</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196" t="s">
+        <v>213</v>
+      </c>
+      <c r="B196">
+        <v>41699</v>
+      </c>
+      <c r="C196">
+        <v>239.09200000000001</v>
+      </c>
+      <c r="D196">
+        <v>0.75310022458319825</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197" t="s">
+        <v>214</v>
+      </c>
+      <c r="B197">
+        <v>41730</v>
+      </c>
+      <c r="C197">
+        <v>239.80799999999999</v>
+      </c>
+      <c r="D197">
+        <v>0.75535550606815616</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198" t="s">
+        <v>215</v>
+      </c>
+      <c r="B198">
+        <v>41760</v>
+      </c>
+      <c r="C198">
+        <v>241.35</v>
+      </c>
+      <c r="D198">
+        <v>0.76021255083045391</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199" t="s">
+        <v>216</v>
+      </c>
+      <c r="B199">
+        <v>41791</v>
+      </c>
+      <c r="C199">
+        <v>241.61600000000001</v>
+      </c>
+      <c r="D199">
+        <v>0.76105040680112268</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200" t="s">
+        <v>217</v>
+      </c>
+      <c r="B200">
+        <v>41821</v>
+      </c>
+      <c r="C200">
+        <v>241.85</v>
+      </c>
+      <c r="D200">
+        <v>0.76178746806855302</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201" t="s">
+        <v>218</v>
+      </c>
+      <c r="B201">
+        <v>41852</v>
+      </c>
+      <c r="C201">
+        <v>241.66</v>
+      </c>
+      <c r="D201">
+        <v>0.76118899951807539</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202" t="s">
+        <v>219</v>
+      </c>
+      <c r="B202">
+        <v>41883</v>
+      </c>
+      <c r="C202">
+        <v>241.92</v>
+      </c>
+      <c r="D202">
+        <v>0.76200795648188691</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203" t="s">
+        <v>220</v>
+      </c>
+      <c r="B203">
+        <v>41913</v>
+      </c>
+      <c r="C203">
+        <v>241.65</v>
+      </c>
+      <c r="D203">
+        <v>0.76115750117331338</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204" t="s">
+        <v>221</v>
+      </c>
+      <c r="B204">
+        <v>41944</v>
+      </c>
+      <c r="C204">
+        <v>240.22</v>
+      </c>
+      <c r="D204">
+        <v>0.75665323787234984</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205" t="s">
+        <v>222</v>
+      </c>
+      <c r="B205">
+        <v>41974</v>
+      </c>
+      <c r="C205">
+        <v>239.095</v>
+      </c>
+      <c r="D205">
+        <v>0.75310967408662677</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206" t="s">
+        <v>223</v>
+      </c>
+      <c r="B206">
+        <v>42005</v>
+      </c>
+      <c r="C206">
+        <v>238.31800000000001</v>
+      </c>
+      <c r="D206">
+        <v>0.75066225269862075</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207" t="s">
+        <v>224</v>
+      </c>
+      <c r="B207">
+        <v>42036</v>
+      </c>
+      <c r="C207">
+        <v>239.74799999999999</v>
+      </c>
+      <c r="D207">
+        <v>0.75516651599958429</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208" t="s">
+        <v>225</v>
+      </c>
+      <c r="B208">
+        <v>42064</v>
+      </c>
+      <c r="C208">
+        <v>241.69</v>
+      </c>
+      <c r="D208">
+        <v>0.76128349455236133</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209" t="s">
+        <v>226</v>
+      </c>
+      <c r="B209">
+        <v>42095</v>
+      </c>
+      <c r="C209">
+        <v>242.30199999999999</v>
+      </c>
+      <c r="D209">
+        <v>0.76321119325179465</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210" t="s">
+        <v>227</v>
+      </c>
+      <c r="B210">
+        <v>42125</v>
+      </c>
+      <c r="C210">
+        <v>244.227</v>
+      </c>
+      <c r="D210">
+        <v>0.7692746246184764</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211" t="s">
+        <v>228</v>
+      </c>
+      <c r="B211">
+        <v>42156</v>
+      </c>
+      <c r="C211">
+        <v>244.33199999999999</v>
+      </c>
+      <c r="D211">
+        <v>0.76960535723847712</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212" t="s">
+        <v>229</v>
+      </c>
+      <c r="B212">
+        <v>42186</v>
+      </c>
+      <c r="C212">
+        <v>245.04</v>
+      </c>
+      <c r="D212">
+        <v>0.7718354400476255</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213" t="s">
+        <v>230</v>
+      </c>
+      <c r="B213">
+        <v>42217</v>
+      </c>
+      <c r="C213">
+        <v>244.73699999999999</v>
+      </c>
+      <c r="D213">
+        <v>0.77088104020133741</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214" t="s">
+        <v>231</v>
+      </c>
+      <c r="B214">
+        <v>42248</v>
+      </c>
+      <c r="C214">
+        <v>244.25700000000001</v>
+      </c>
+      <c r="D214">
+        <v>0.76936911965276233</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215" t="s">
+        <v>232</v>
+      </c>
+      <c r="B215">
+        <v>42278</v>
+      </c>
+      <c r="C215">
+        <v>244.34100000000001</v>
+      </c>
+      <c r="D215">
+        <v>0.769633705748763</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216" t="s">
+        <v>233</v>
+      </c>
+      <c r="B216">
+        <v>42309</v>
+      </c>
+      <c r="C216">
+        <v>243.749</v>
+      </c>
+      <c r="D216">
+        <v>0.76776900373885359</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217" t="s">
+        <v>234</v>
+      </c>
+      <c r="B217">
+        <v>42339</v>
+      </c>
+      <c r="C217">
+        <v>243.434</v>
+      </c>
+      <c r="D217">
+        <v>0.76677680587885111</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218" t="s">
+        <v>235</v>
+      </c>
+      <c r="B218">
+        <v>42370</v>
+      </c>
+      <c r="C218">
+        <v>244.6</v>
+      </c>
+      <c r="D218">
+        <v>0.77044951287809826</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219" t="s">
+        <v>236</v>
+      </c>
+      <c r="B219">
+        <v>42401</v>
+      </c>
+      <c r="C219">
+        <v>244.821</v>
+      </c>
+      <c r="D219">
+        <v>0.77114562629733818</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>237</v>
+      </c>
+      <c r="B220">
+        <v>42430</v>
+      </c>
+      <c r="C220">
+        <v>245.404</v>
+      </c>
+      <c r="D220">
+        <v>0.7729819797969617</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>238</v>
+      </c>
+      <c r="B221">
+        <v>42461</v>
+      </c>
+      <c r="C221">
+        <v>246.589</v>
+      </c>
+      <c r="D221">
+        <v>0.77671453365125664</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>239</v>
+      </c>
+      <c r="B222">
+        <v>42491</v>
+      </c>
+      <c r="C222">
+        <v>247.85499999999999</v>
+      </c>
+      <c r="D222">
+        <v>0.78070222409812362</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223" t="s">
+        <v>240</v>
+      </c>
+      <c r="B223">
+        <v>42522</v>
+      </c>
+      <c r="C223">
+        <v>248.22800000000001</v>
+      </c>
+      <c r="D223">
+        <v>0.78187711235774571</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" t="s">
+        <v>241</v>
+      </c>
+      <c r="B224">
+        <v>42552</v>
+      </c>
+      <c r="C224">
+        <v>248.375</v>
+      </c>
+      <c r="D224">
+        <v>0.78234013802574676</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" t="s">
+        <v>242</v>
+      </c>
+      <c r="B225">
+        <v>42583</v>
+      </c>
+      <c r="C225">
+        <v>248.49799999999999</v>
+      </c>
+      <c r="D225">
+        <v>0.78272756766631912</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" t="s">
+        <v>243</v>
+      </c>
+      <c r="B226">
+        <v>42614</v>
+      </c>
+      <c r="C226">
+        <v>249.23400000000001</v>
+      </c>
+      <c r="D226">
+        <v>0.78504584584080117</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>244</v>
+      </c>
+      <c r="B227">
+        <v>42644</v>
+      </c>
+      <c r="C227">
+        <v>249.89699999999999</v>
+      </c>
+      <c r="D227">
+        <v>0.78713418609852059</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>245</v>
+      </c>
+      <c r="B228">
+        <v>42675</v>
+      </c>
+      <c r="C228">
+        <v>249.44800000000001</v>
+      </c>
+      <c r="D228">
+        <v>0.78571991041870759</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>246</v>
+      </c>
+      <c r="B229">
+        <v>42705</v>
+      </c>
+      <c r="C229">
+        <v>249.51599999999999</v>
+      </c>
+      <c r="D229">
+        <v>0.78593409916308898</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>247</v>
+      </c>
+      <c r="B230">
+        <v>42736</v>
+      </c>
+      <c r="C230">
+        <v>250.81399999999999</v>
+      </c>
+      <c r="D230">
+        <v>0.79002258431319439</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>248</v>
+      </c>
+      <c r="B231">
+        <v>42767</v>
+      </c>
+      <c r="C231">
+        <v>252.25200000000001</v>
+      </c>
+      <c r="D231">
+        <v>0.79455204628996756</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>249</v>
+      </c>
+      <c r="B232">
+        <v>42795</v>
+      </c>
+      <c r="C232">
+        <v>252.94900000000001</v>
+      </c>
+      <c r="D232">
+        <v>0.79674748091987779</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>250</v>
+      </c>
+      <c r="B233">
+        <v>42826</v>
+      </c>
+      <c r="C233">
+        <v>253.80600000000001</v>
+      </c>
+      <c r="D233">
+        <v>0.79944688906597972</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>251</v>
+      </c>
+      <c r="B234">
+        <v>42856</v>
+      </c>
+      <c r="C234">
+        <v>254.38</v>
+      </c>
+      <c r="D234">
+        <v>0.80125489405531747</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>252</v>
+      </c>
+      <c r="B235">
+        <v>42887</v>
+      </c>
+      <c r="C235">
+        <v>254.46899999999999</v>
+      </c>
+      <c r="D235">
+        <v>0.80153522932369903</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>253</v>
+      </c>
+      <c r="B236">
+        <v>42917</v>
+      </c>
+      <c r="C236">
+        <v>254.708</v>
+      </c>
+      <c r="D236">
+        <v>0.80228803976351049</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>254</v>
+      </c>
+      <c r="B237">
+        <v>42948</v>
+      </c>
+      <c r="C237">
+        <v>255.28200000000001</v>
+      </c>
+      <c r="D237">
+        <v>0.80409604475284835</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>255</v>
+      </c>
+      <c r="B238">
+        <v>42979</v>
+      </c>
+      <c r="C238">
+        <v>256.50400000000002</v>
+      </c>
+      <c r="D238">
+        <v>0.80794514248276261</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239" t="s">
+        <v>256</v>
+      </c>
+      <c r="B239">
+        <v>43009</v>
+      </c>
+      <c r="C239">
+        <v>257.22300000000001</v>
+      </c>
+      <c r="D239">
+        <v>0.81020987347114914</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240" t="s">
+        <v>257</v>
+      </c>
+      <c r="B240">
+        <v>43040</v>
+      </c>
+      <c r="C240">
+        <v>257.12599999999998</v>
+      </c>
+      <c r="D240">
+        <v>0.80990433952695784</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241" t="s">
+        <v>258</v>
+      </c>
+      <c r="B241">
+        <v>43070</v>
+      </c>
+      <c r="C241">
+        <v>257.34699999999998</v>
+      </c>
+      <c r="D241">
+        <v>0.81060045294619765</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242" t="s">
+        <v>259</v>
+      </c>
+      <c r="B242">
+        <v>43101</v>
+      </c>
+      <c r="C242">
+        <v>258.63799999999998</v>
+      </c>
+      <c r="D242">
+        <v>0.81466688925496966</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243" t="s">
+        <v>260</v>
+      </c>
+      <c r="B243">
+        <v>43132</v>
+      </c>
+      <c r="C243">
+        <v>259.98599999999999</v>
+      </c>
+      <c r="D243">
+        <v>0.81891286612888492</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244" t="s">
+        <v>261</v>
+      </c>
+      <c r="B244">
+        <v>43160</v>
+      </c>
+      <c r="C244">
+        <v>260.99400000000003</v>
+      </c>
+      <c r="D244">
+        <v>0.82208789928089299</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245" t="s">
+        <v>262</v>
+      </c>
+      <c r="B245">
+        <v>43191</v>
+      </c>
+      <c r="C245">
+        <v>262.03699999999998</v>
+      </c>
+      <c r="D245">
+        <v>0.82537317663956755</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246" t="s">
+        <v>263</v>
+      </c>
+      <c r="B246">
+        <v>43221</v>
+      </c>
+      <c r="C246">
+        <v>263.24</v>
+      </c>
+      <c r="D246">
+        <v>0.82916242751443425</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247" t="s">
+        <v>264</v>
+      </c>
+      <c r="B247">
+        <v>43252</v>
+      </c>
+      <c r="C247">
+        <v>263.73200000000003</v>
+      </c>
+      <c r="D247">
+        <v>0.83071214607672383</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248" t="s">
+        <v>265</v>
+      </c>
+      <c r="B248">
+        <v>43282</v>
+      </c>
+      <c r="C248">
+        <v>263.971</v>
+      </c>
+      <c r="D248">
+        <v>0.83146495651653518</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249" t="s">
+        <v>266</v>
+      </c>
+      <c r="B249">
+        <v>43313</v>
+      </c>
+      <c r="C249">
+        <v>264.39499999999998</v>
+      </c>
+      <c r="D249">
+        <v>0.83280048633444315</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250" t="s">
+        <v>267</v>
+      </c>
+      <c r="B250">
+        <v>43344</v>
+      </c>
+      <c r="C250">
+        <v>265.10500000000002</v>
+      </c>
+      <c r="D250">
+        <v>0.83503686881254402</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251" t="s">
+        <v>268</v>
+      </c>
+      <c r="B251">
+        <v>43374</v>
+      </c>
+      <c r="C251">
+        <v>266.19499999999999</v>
+      </c>
+      <c r="D251">
+        <v>0.83847018839160004</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252" t="s">
+        <v>269</v>
+      </c>
+      <c r="B252">
+        <v>43405</v>
+      </c>
+      <c r="C252">
+        <v>265.65800000000002</v>
+      </c>
+      <c r="D252">
+        <v>0.83677872727788161</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253" t="s">
+        <v>270</v>
+      </c>
+      <c r="B253">
+        <v>43435</v>
+      </c>
+      <c r="C253">
+        <v>265.209</v>
+      </c>
+      <c r="D253">
+        <v>0.8353644515980686</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254" t="s">
+        <v>271</v>
+      </c>
+      <c r="B254">
+        <v>43466</v>
+      </c>
+      <c r="C254">
+        <v>265.62400000000002</v>
+      </c>
+      <c r="D254">
+        <v>0.83667163290569091</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255" t="s">
+        <v>272</v>
+      </c>
+      <c r="B255">
+        <v>43497</v>
+      </c>
+      <c r="C255">
+        <v>266.21499999999997</v>
+      </c>
+      <c r="D255">
+        <v>0.83853318508112396</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256" t="s">
+        <v>273</v>
+      </c>
+      <c r="B256">
+        <v>43525</v>
+      </c>
+      <c r="C256">
+        <v>267.37</v>
+      </c>
+      <c r="D256">
+        <v>0.84217124390113307</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257" t="s">
+        <v>274</v>
+      </c>
+      <c r="B257">
+        <v>43556</v>
+      </c>
+      <c r="C257">
+        <v>269.52199999999999</v>
+      </c>
+      <c r="D257">
+        <v>0.84894968769391177</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258" t="s">
+        <v>275</v>
+      </c>
+      <c r="B258">
+        <v>43586</v>
+      </c>
+      <c r="C258">
+        <v>270.88</v>
+      </c>
+      <c r="D258">
+        <v>0.85322716291258904</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259" t="s">
+        <v>276</v>
+      </c>
+      <c r="B259">
+        <v>43617</v>
+      </c>
+      <c r="C259">
+        <v>270.95699999999999</v>
+      </c>
+      <c r="D259">
+        <v>0.85346970016725621</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260" t="s">
+        <v>277</v>
+      </c>
+      <c r="B260">
+        <v>43647</v>
+      </c>
+      <c r="C260">
+        <v>271.029</v>
+      </c>
+      <c r="D260">
+        <v>0.85369648824954258</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261" t="s">
+        <v>278</v>
+      </c>
+      <c r="B261">
+        <v>43678</v>
+      </c>
+      <c r="C261">
+        <v>271.26400000000001</v>
+      </c>
+      <c r="D261">
+        <v>0.85443669935144917</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262" t="s">
+        <v>279</v>
+      </c>
+      <c r="B262">
+        <v>43709</v>
+      </c>
+      <c r="C262">
+        <v>272.10199999999998</v>
+      </c>
+      <c r="D262">
+        <v>0.8570762606425032</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263" t="s">
+        <v>280</v>
+      </c>
+      <c r="B263">
+        <v>43739</v>
+      </c>
+      <c r="C263">
+        <v>273.524</v>
+      </c>
+      <c r="D263">
+        <v>0.86155532526765721</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
+        <v>281</v>
+      </c>
+      <c r="B264">
+        <v>43770</v>
+      </c>
+      <c r="C264">
+        <v>273.12799999999999</v>
+      </c>
+      <c r="D264">
+        <v>0.86030799081508269</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265" t="s">
+        <v>282</v>
+      </c>
+      <c r="B265">
+        <v>43800</v>
+      </c>
+      <c r="C265">
+        <v>272.584</v>
+      </c>
+      <c r="D265">
+        <v>0.85859448086003087</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
+        <v>283</v>
+      </c>
+      <c r="B266">
+        <v>43831</v>
+      </c>
+      <c r="C266">
+        <v>273.33999999999997</v>
+      </c>
+      <c r="D266">
+        <v>0.86097575572403673</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267" t="s">
+        <v>284</v>
+      </c>
+      <c r="B267">
+        <v>43862</v>
+      </c>
+      <c r="C267">
+        <v>274.41199999999998</v>
+      </c>
+      <c r="D267">
+        <v>0.86435237828252121</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268" t="s">
+        <v>285</v>
+      </c>
+      <c r="B268">
+        <v>43891</v>
+      </c>
+      <c r="C268">
+        <v>273.995</v>
+      </c>
+      <c r="D268">
+        <v>0.86303889730594663</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269" t="s">
+        <v>286</v>
+      </c>
+      <c r="B269">
+        <v>43922</v>
+      </c>
+      <c r="C269">
+        <v>272.91300000000001</v>
+      </c>
+      <c r="D269">
+        <v>0.85963077640270014</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270" t="s">
+        <v>287</v>
+      </c>
+      <c r="B270">
+        <v>43952</v>
+      </c>
+      <c r="C270">
+        <v>273.06200000000001</v>
+      </c>
+      <c r="D270">
+        <v>0.86010010173965368</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271" t="s">
+        <v>288</v>
+      </c>
+      <c r="B271">
+        <v>43983</v>
+      </c>
+      <c r="C271">
+        <v>274.15499999999997</v>
+      </c>
+      <c r="D271">
+        <v>0.86354287082213832</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
+        <v>289</v>
+      </c>
+      <c r="B272">
+        <v>44013</v>
+      </c>
+      <c r="C272">
+        <v>275.59699999999998</v>
+      </c>
+      <c r="D272">
+        <v>0.86808493213681626</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>290</v>
+      </c>
+      <c r="B273">
+        <v>44044</v>
+      </c>
+      <c r="C273">
+        <v>276.44299999999998</v>
+      </c>
+      <c r="D273">
+        <v>0.87074969210367992</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274" t="s">
+        <v>291</v>
+      </c>
+      <c r="B274">
+        <v>44075</v>
+      </c>
+      <c r="C274">
+        <v>276.42200000000003</v>
+      </c>
+      <c r="D274">
+        <v>0.87068354557967997</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275" t="s">
+        <v>292</v>
+      </c>
+      <c r="B275">
+        <v>44105</v>
+      </c>
+      <c r="C275">
+        <v>276.87599999999998</v>
+      </c>
+      <c r="D275">
+        <v>0.87211357043187376</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276" t="s">
+        <v>293</v>
+      </c>
+      <c r="B276">
+        <v>44136</v>
+      </c>
+      <c r="C276">
+        <v>276.875</v>
+      </c>
+      <c r="D276">
+        <v>0.87211042059739763</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277" t="s">
+        <v>294</v>
+      </c>
+      <c r="B277">
+        <v>44166</v>
+      </c>
+      <c r="C277">
+        <v>276.59300000000002</v>
+      </c>
+      <c r="D277">
+        <v>0.87122216727510982</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278" t="s">
+        <v>295</v>
+      </c>
+      <c r="B278">
+        <v>44197</v>
+      </c>
+      <c r="C278">
+        <v>277.238</v>
+      </c>
+      <c r="D278">
+        <v>0.8732538105122577</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
+        <v>296</v>
+      </c>
+      <c r="B279">
+        <v>44228</v>
+      </c>
+      <c r="C279">
+        <v>278.702</v>
+      </c>
+      <c r="D279">
+        <v>0.87786516818541194</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
+        <v>297</v>
+      </c>
+      <c r="B280">
+        <v>44256</v>
+      </c>
+      <c r="C280">
+        <v>280.625</v>
+      </c>
+      <c r="D280">
+        <v>0.88392229988314119</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281" t="s">
+        <v>298</v>
+      </c>
+      <c r="B281">
+        <v>44287</v>
+      </c>
+      <c r="C281">
+        <v>283.50700000000001</v>
+      </c>
+      <c r="D281">
+        <v>0.89300012284354469</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282" t="s">
+        <v>299</v>
+      </c>
+      <c r="B282">
+        <v>44317</v>
+      </c>
+      <c r="C282">
+        <v>285.79300000000001</v>
+      </c>
+      <c r="D282">
+        <v>0.9002006444561339</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283" t="s">
+        <v>300</v>
+      </c>
+      <c r="B283">
+        <v>44348</v>
+      </c>
+      <c r="C283">
+        <v>288.26299999999998</v>
+      </c>
+      <c r="D283">
+        <v>0.9079807356123436</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284" t="s">
+        <v>301</v>
+      </c>
+      <c r="B284">
+        <v>44378</v>
+      </c>
+      <c r="C284">
+        <v>289.863</v>
+      </c>
+      <c r="D284">
+        <v>0.91302047077426085</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285" t="s">
+        <v>302</v>
+      </c>
+      <c r="B285">
+        <v>44409</v>
+      </c>
+      <c r="C285">
+        <v>290.39299999999997</v>
+      </c>
+      <c r="D285">
+        <v>0.91468988304664589</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286" t="s">
+        <v>303</v>
+      </c>
+      <c r="B286">
+        <v>44440</v>
+      </c>
+      <c r="C286">
+        <v>291.053</v>
+      </c>
+      <c r="D286">
+        <v>0.9167687738009368</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287" t="s">
+        <v>304</v>
+      </c>
+      <c r="B287">
+        <v>44470</v>
+      </c>
+      <c r="C287">
+        <v>293.39699999999999</v>
+      </c>
+      <c r="D287">
+        <v>0.92415198581314562</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288" t="s">
+        <v>305</v>
+      </c>
+      <c r="B288">
+        <v>44501</v>
+      </c>
+      <c r="C288">
+        <v>294.98599999999999</v>
+      </c>
+      <c r="D288">
+        <v>0.9291570727958246</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289" t="s">
+        <v>306</v>
+      </c>
+      <c r="B289">
+        <v>44531</v>
+      </c>
+      <c r="C289">
+        <v>296.10199999999998</v>
+      </c>
+      <c r="D289">
+        <v>0.9326722880712619</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290" t="s">
+        <v>307</v>
+      </c>
+      <c r="B290">
+        <v>44562</v>
+      </c>
+      <c r="C290">
+        <v>298.70499999999998</v>
+      </c>
+      <c r="D290">
+        <v>0.94087130721280599</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291" t="s">
+        <v>308</v>
+      </c>
+      <c r="B291">
+        <v>44593</v>
+      </c>
+      <c r="C291">
+        <v>301.15800000000002</v>
+      </c>
+      <c r="D291">
+        <v>0.9485978511829205</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292" t="s">
+        <v>309</v>
+      </c>
+      <c r="B292">
+        <v>44621</v>
+      </c>
+      <c r="C292">
+        <v>305.08199999999999</v>
+      </c>
+      <c r="D292">
+        <v>0.96095780166752243</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293" t="s">
+        <v>310</v>
+      </c>
+      <c r="B293">
+        <v>44652</v>
+      </c>
+      <c r="C293">
+        <v>307.14499999999998</v>
+      </c>
+      <c r="D293">
+        <v>0.96745591019191945</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294" t="s">
+        <v>311</v>
+      </c>
+      <c r="B294">
+        <v>44682</v>
+      </c>
+      <c r="C294">
+        <v>309.64499999999998</v>
+      </c>
+      <c r="D294">
+        <v>0.97533049638241509</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295" t="s">
+        <v>312</v>
+      </c>
+      <c r="B295">
+        <v>44713</v>
+      </c>
+      <c r="C295">
+        <v>313.49599999999998</v>
+      </c>
+      <c r="D295">
+        <v>0.98746050895025472</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296" t="s">
+        <v>313</v>
+      </c>
+      <c r="B296">
+        <v>44743</v>
+      </c>
+      <c r="C296">
+        <v>313.95100000000002</v>
+      </c>
+      <c r="D296">
+        <v>0.98889368363692498</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297" t="s">
+        <v>314</v>
+      </c>
+      <c r="B297">
+        <v>44774</v>
+      </c>
+      <c r="C297">
+        <v>314.01299999999998</v>
+      </c>
+      <c r="D297">
+        <v>0.98908897337444912</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298" t="s">
+        <v>315</v>
+      </c>
+      <c r="B298">
+        <v>44805</v>
+      </c>
+      <c r="C298">
+        <v>315.09399999999999</v>
+      </c>
+      <c r="D298">
+        <v>0.99249394444321959</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299" t="s">
+        <v>316</v>
+      </c>
+      <c r="B299">
+        <v>44835</v>
+      </c>
+      <c r="C299">
+        <v>317.29899999999998</v>
+      </c>
+      <c r="D299">
+        <v>0.99943932946323677</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300" t="s">
+        <v>317</v>
+      </c>
+      <c r="B300">
+        <v>44866</v>
+      </c>
+      <c r="C300">
+        <v>315.91899999999998</v>
+      </c>
+      <c r="D300">
+        <v>0.99509255788608308</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301" t="s">
+        <v>318</v>
+      </c>
+      <c r="B301">
+        <v>44896</v>
+      </c>
+      <c r="C301">
+        <v>314.59899999999999</v>
+      </c>
+      <c r="D301">
+        <v>0.99093477637750138</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302" t="s">
+        <v>319</v>
+      </c>
+      <c r="B302">
+        <v>44927</v>
+      </c>
+      <c r="C302">
+        <v>317.47699999999998</v>
+      </c>
+      <c r="D302">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
+++ b/Indicator_Gen/config/CPI Inflation Adjustment Factors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfontes\Documents\Projects\Regional-Monitoring\Indicator_Gen\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AD5063-4570-4281-949D-EFD520465851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC6CAF0D-8AAE-4F73-AB21-285F32C62284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sources" sheetId="7" r:id="rId1"/>
